--- a/marketer_forms/011_high_heels_market_survey--marketer_forms.xlsx
+++ b/marketer_forms/011_high_heels_market_survey--marketer_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -776,7 +776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1331,17 +1331,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>favorite_color_choices</t>
+          <t>purchase_channel_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>brown</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brown</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1353,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>online</t>
+          <t>in_store</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>In Store</t>
         </is>
       </c>
     </row>
@@ -1370,12 +1370,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>in_store</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>In Store</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1387,12 +1387,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>mail_order</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Mail Order</t>
         </is>
       </c>
     </row>
@@ -1404,29 +1404,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>mail_order</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mail Order</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>purchase_channel_choices</t>
+          <t>customer_satisfaction_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -1455,12 +1455,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>somewhat_satisfied</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Somewhat Satisfied</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1489,27 +1489,10 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>somewhat_dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
-        <is>
-          <t>Somewhat Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>customer_satisfaction_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>very_dissatisfied</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
         <is>
           <t>Very Dissatisfied</t>
         </is>
